--- a/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
+++ b/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="估算使用说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="持仓明细" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="资产配置" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="地区行业" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="对比摘要" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="后续跟踪模板" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="重点观察标的" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="默认估算持仓" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="估算模型校验" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估算使用说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产配置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地区行业" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对比摘要" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续跟踪模板" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重点观察标的" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="默认估算持仓" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估算模型校验" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'说明'!$A$1:$B$10</definedName>
@@ -223,13 +223,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -253,7 +253,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -277,7 +277,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -305,8 +305,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -332,8 +332,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -359,7 +359,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -374,9 +374,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21 20:09:15</t>
+          <t>2026-06-28 20:15:12</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11至2026-06-17：A份额累计+8.22%，C份额累计+8.22%；已追加日度拟合。</t>
+          <t>2026-06-18至2026-06-25：A份额累计+5.93%，C份额累计+5.92%；Q1可见持仓+CSOP估算约+2.05%，误差-3.87pct。</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>截至本次运行，天天基金公告接口最新定期报告仍为2026年第1季度报告（2026-04-22，AN202604211821382912）；无新增季报/半年报/年报。</t>
+          <t>截至2026-06-28，天天基金/东方财富定期报告接口最新仍为天弘全球新能源汽车股票型证券投资基金(QDII-LOF)2026年第1季度报告（2026-04-22，AN202604211821382912）；未发现新的季报、半年报或年报。</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>使用2026Q1前十大股票及CSOP 07709.HK、07747.HK可见权重，叠加Yahoo历史价格与USD/CNY、HKD/CNY；季度报告非全持仓披露。</t>
+          <t>使用2026Q1前十大股票及CSOP 07709.HK、07747.HK/09747.HK可见权重（合计约41.15%），叠加Yahoo历史价格与USD/CNY、HKD/CNY；季度报告非全量权益持仓披露。</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9215,6 +9215,266 @@
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2.5966</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>KLAC/TSM/TER/7709.HK</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>可见Q1持仓方向与公布净值一致，但强度不足；缺口来自未披露持仓、调仓、杠杆或时点差异。</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2.6711</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2.6457</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7709.HK/COHR/LITE/LRCX</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>AVGO/NVDA/7747.HK</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>可见Q1持仓方向与公布净值一致，但强度不足；缺口来自未披露持仓、调仓、杠杆或时点差异。</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2.4823</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2.4587</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>无明显可见重仓正贡献</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7709.HK/COHR/KLAC/7747.HK</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>可见AI链与两只CSOP 2x同步回撤；公布跌幅更深，提示未披露仓位或调仓放大下行。</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2.5392</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2.5151</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7747.HK/7709.HK/COHR/LITE</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>KLAC/TSLA/NVDA</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>可见Q1持仓方向与公布净值一致，但强度不足；缺口来自未披露持仓、调仓、杠杆或时点差异。</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2.6419</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2.6167</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7709.HK/TER/KLAC/LRCX</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>NVDA/TSM/AVGO/TSLA</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>可见Q1持仓方向与公布净值一致，但强度不足；缺口来自未披露持仓、调仓、杠杆或时点差异。</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
         </is>

--- a/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
+++ b/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28 20:15:12</t>
+          <t>2026-07-05 20:10:38</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18至2026-06-25：A份额累计+5.93%，C份额累计+5.92%；Q1可见持仓+CSOP估算约+2.05%，误差-3.87pct。</t>
+          <t>2026-06-26至2026-07-02：A份额累计-11.51%，C份额累计-11.51%；Q1前十大+CSOP可见仓位估算约-4.45%，误差+7.05pct（估算跌幅不足）。</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>截至2026-06-28，天天基金/东方财富定期报告接口最新仍为天弘全球新能源汽车股票型证券投资基金(QDII-LOF)2026年第1季度报告（2026-04-22，AN202604211821382912）；未发现新的季报、半年报或年报。</t>
+          <t>截至2026-07-05，天天基金/东方财富定期报告接口最新仍为天弘全球新能源汽车股票型证券投资基金(QDII-LOF)2026年第1季度报告（2026-04-22，AN202604211821382912）；未发现新的季报、半年报或年报。</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>使用2026Q1前十大股票及CSOP 07709.HK、07747.HK/09747.HK可见权重（合计约41.15%），叠加Yahoo历史价格与USD/CNY、HKD/CNY；季度报告非全量权益持仓披露。</t>
+          <t>使用2026Q1前十大股票及CSOP 07709.HK、07747.HK/09747.HK可见权重（合计约41.15%），叠加Yahoo历史价格与USD/CNY、HKD/CNY；港股休市日以前值填充；季度报告非全量权益持仓披露。</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9475,6 +9475,266 @@
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2.5284</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2.5043</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7709.HK/TER/COHR/LITE</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>可见AI硬件链与CSOP 2x同步回撤，但公布跌幅更深；缺口来自未披露持仓、调仓、估值或时点差异。</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2.5988</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>KLAC/TSLA/LRCX/TER</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7709.HK/7747.HK</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>美股AI硬件链反弹，CSOP 2x继续拖累；估算低于公布涨幅。</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>2.6734</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2.6478</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>KLAC/AMD/TSM/LRCX</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>无明显可见重仓拖累</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Q1可见AI链普涨，方向与公布净值一致但强度不足。</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2.5612</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2.5367</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>TER/KLAC/LRCX/TSM</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>港股7月1日休市，CSOP按前值处理；美股半导体设备和光通信回撤主导。</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2.3379</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2.3155</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>无明显可见重仓正贡献</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7709.HK/TER/KLAC/LITE</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>可见AI链与两只CSOP 2x大幅回撤，但公布跌幅明显更深；提示未披露仓位、调仓或估值时点差异显著。</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>ttskill NAV + Yahoo chart + USD/CNY/HKD/CNY</t>
         </is>

--- a/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
+++ b/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重点观察标的" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="默认估算持仓" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估算模型校验" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓基金公告检查" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'说明'!$A$1:$B$10</definedName>
@@ -36,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +56,13 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="6">
@@ -111,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +152,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -790,11 +810,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,7 +837,7 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Q2新增外部持仓_误差0点2以内组合</t>
+          <t>2026Q2正式披露锚点_剩余权益待重拟合</t>
         </is>
       </c>
     </row>
@@ -829,7 +849,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>active_default</t>
+          <t>official_anchor_pending_refit</t>
         </is>
       </c>
     </row>
@@ -853,7 +873,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>2026-06-22净值日之后的日常估算，直到下一次披露或重新拟合</t>
+          <t>2026-06-30报告期之后；日常估算先用Q2官方锚点，剩余未披露权益需重新拟合</t>
         </is>
       </c>
     </row>
@@ -865,7 +885,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\天弘全球新能源汽车QDII_LOF_Q2新增外部持仓_误差0点2以内组合_20260622.xlsx</t>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx</t>
         </is>
       </c>
     </row>
@@ -887,8 +907,10 @@
           <t>最大回测误差pct</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
-        <v>0.1606780811368211</v>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>N/A（Q2正式披露锚点尚未重新拟合）</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -912,6 +934,30 @@
       <c r="B10" s="10" t="inlineStr">
         <is>
           <t>后续估算默认读取“默认估算持仓”或JSON；固定Q1前十大+两只ETF，剩余个股使用本次Q2外部候选拟合权重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>上一版拟合基准</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Q2新增外部持仓_误差0点2以内组合；已被2026Q2正式披露部分替代，历史校验留存。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Q2官方披露来源</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
         </is>
       </c>
     </row>
@@ -1254,21 +1300,469 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>检查时间</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>基金代码</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>基金名称</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>最新定期报告公告</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>公告发布日期</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ttskill持仓报告日</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>是否发现新持仓披露</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>更新动作</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>来源链接</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票型证券投资基金(QDII-LOF)2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>已更新164212跟踪表Q2持仓/配置/观察/估算锚点</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>016823</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)C</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票型证券投资基金(QDII-LOF)2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>同一投资组合；已随164212更新</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>100055</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>富国全球科技互联网股票(QDII)A</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>富国全球科技互联网股票型证券投资基金(QDII)二0二六年第1季度报告</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>https://fundf10.eastmoney.com/jjgg_100055.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>022184</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>富国全球科技互联网股票(QDII)C</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>富国全球科技互联网股票型证券投资基金(QDII)二0二六年第1季度报告</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>https://fundf10.eastmoney.com/jjgg_022184.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>017730</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>嘉实全球产业升级股票发起式(QDII)A</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>嘉实全球产业升级股票型发起式证券投资基金(QDII)2026年第1季度报告</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>https://fundf10.eastmoney.com/jjgg_017730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>017731</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>嘉实全球产业升级股票发起式(QDII)C</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>嘉实全球产业升级股票型发起式证券投资基金(QDII)2026年第1季度报告</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>https://fundf10.eastmoney.com/jjgg_017731.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>016664</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球高端制造混合(QDII)A</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球高端制造混合型证券投资基金(QDII)2026年第1季度报告</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>https://fundf10.eastmoney.com/jjgg_016664.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>016665</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球高端制造混合(QDII)C</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>天弘全球高端制造混合型证券投资基金(QDII)2026年第1季度报告</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>https://fundf10.eastmoney.com/jjgg_016665.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>天弘全球新能源汽车股票(QDII-LOF) A/C 持仓跟踪表</t>
         </is>
@@ -1283,7 +1777,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05 20:10:38</t>
+          <t>2026-07-20 21:53:45</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1801,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2025年报已持有AI/半导体/智能化仓位；2026Q1进一步转向AI硬件、半导体设备、光通信和存储链，并新增两只CSOP 2x产品。</t>
+          <t>2026Q2已披露：组合更明确聚焦AI算力上游/半导体/存储链；前十大转为GLW/MRVL/MU/AMD/TER/LITE/AMAT/COHR/STM/华虹；两只CSOP 2x仍在且合计净值占比6.77%。</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1813,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2025年报披露全部权益持仓；2026Q1只披露前十大股票/存托凭证、基金投资、债券、行业/地区配置，不披露全部股票。</t>
+          <t>2026Q2季报仍只披露前十大股票/存托凭证、基金投资、债券、行业/地区配置，不披露全部股票；剩余权益约57.05%为未披露。</t>
         </is>
       </c>
     </row>
@@ -1421,50 +1915,98 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>默认估算持仓启用</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>2026-06-23 23:43:08</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>默认估算持仓来源</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\天弘全球新能源汽车QDII_LOF_Q2新增外部持仓_误差0点2以内组合_20260622.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>机器可读基准</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\default_estimation_holdings_164212.json</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>估算基准说明</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>后续日常估算164212/016823净值变化时，默认使用“默认估算持仓”sheet/JSON，直到新披露或重新拟合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Q2来源</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>本地Q2 PDF</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>公告检查时间</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:53:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>其他持仓基金公告检查</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>见“持仓基金公告检查”sheet；截至本次检查，富国全球科技互联网、嘉实全球产业升级、天弘全球高端制造最新持仓披露仍为2026Q1。</t>
         </is>
       </c>
     </row>
@@ -1480,152 +2022,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="38" customWidth="1" min="23" max="23"/>
-    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>基金代码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>基金名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>报告期</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>报告日期</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>报告类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>披露范围</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>资产类别</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>英文名</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>代码/ISIN</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>交易市场</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>国家/地区</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="12" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="12" t="inlineStr">
         <is>
           <t>公允价值人民币</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>占基金资产净值%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="12" t="inlineStr">
         <is>
           <t>较上期变化类型</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>较上期变化pct</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="12" t="inlineStr">
         <is>
           <t>产业链桶</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="12" t="inlineStr">
         <is>
           <t>主题归类</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="12" t="inlineStr">
         <is>
           <t>网页来源</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="12" t="inlineStr">
         <is>
           <t>本地PDF</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="12" t="inlineStr">
         <is>
           <t>来源位置</t>
         </is>
@@ -7344,6 +7886,1456 @@
       <c r="X55" s="2" t="inlineStr">
         <is>
           <t>2026Q1债券投资明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>康宁(Corning)</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Corning Inc</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>GLW / US2193501051</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>纽约证券交易所</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>55000</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>95683950.29000001</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>光通信/玻璃材料</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>迈威尔科技</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Marvell Technology Inc</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>MRVL / US5738741041</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>纳斯达克证券交易所</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>39200</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>79532840.84</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>ASIC/高速互联芯片</t>
+        </is>
+      </c>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>美光科技</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Micron Technology Inc</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>MU / US5951121038</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>纳斯达克证券交易所</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>9700</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>76259011.48</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>存储/HBM</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>美国超威半导体公司</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices Inc</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>AMD / US0079031078</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>纳斯达克证券交易所</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>63304318.7</v>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>AI算力/半导体</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>泰瑞达</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Teradyne Inc</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>TER / US8807701029</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>纳斯达克证券交易所</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>42840016.13</v>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>减持</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>半导体测试设备</t>
+        </is>
+      </c>
+      <c r="T60" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Lumentum Holdings Inc</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>LITE / US55024U1097</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>纳斯达克证券交易所</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>42077958.15</v>
+      </c>
+      <c r="P61" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>减持</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>光通信/激光器</t>
+        </is>
+      </c>
+      <c r="T61" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>应用材料</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Applied Materials Inc</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>AMAT / US0382221051</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>纳斯达克证券交易所</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>41856385.95</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>半导体设备</t>
+        </is>
+      </c>
+      <c r="T62" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Coherent Corp</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>COHR / US19247G1076</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>纽约证券交易所</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>14500</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>38957087.98</v>
+      </c>
+      <c r="P63" s="5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>减持</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>光通信/材料器件</t>
+        </is>
+      </c>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>意法半导体</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>STMicroelectronics NV</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>STM / US8610121027</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>纽约证券交易所</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>74000</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>37745054.27</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>功率半导体/车规芯片</t>
+        </is>
+      </c>
+      <c r="T64" s="3" t="inlineStr">
+        <is>
+          <t>智能汽车/AI产业链</t>
+        </is>
+      </c>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>权益</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>华虹半导体有限公司</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Hua Hong Grace Semiconductor Ltd</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>01347.HK / HK0000218211</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>香港证券交易所</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>中国香港</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O65" s="4" t="n">
+        <v>37382392</v>
+      </c>
+      <c r="P65" s="5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>特色工艺/功率半导体</t>
+        </is>
+      </c>
+      <c r="T65" s="3" t="inlineStr">
+        <is>
+          <t>智能汽车/AI产业链</t>
+        </is>
+      </c>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>Q2不披露全部股票；此处只记录报告披露项</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十大股票及存托凭证</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>基金投资</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>CSOP SK Hynix Daily 2x Leveraged Product</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>CSOP SK Hynix Daily 2x Leveraged Product</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>7709.HK</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>香港证券交易所</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>中国香港/韩国半导体敞口</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="n"/>
+      <c r="O66" s="4" t="n">
+        <v>93178044</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="S66" s="3" t="inlineStr">
+        <is>
+          <t>存储/HBM杠杆产品</t>
+        </is>
+      </c>
+      <c r="T66" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>二季报正文未列港股代码；代码沿用此前HKEX/CSOP核验</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十名基金投资明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>季度披露-前十大股票/基金投资</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>基金投资</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>CSOP Samsung Electronics Daily 2x Leveraged Product</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>CSOP Samsung Electronics Daily 2x Leveraged Product</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>7747.HK / 9747.HK</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>香港证券交易所</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>中国香港/韩国半导体敞口</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="n"/>
+      <c r="O67" s="4" t="n">
+        <v>36370531.25</v>
+      </c>
+      <c r="P67" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>存储/半导体杠杆产品</t>
+        </is>
+      </c>
+      <c r="T67" s="3" t="inlineStr">
+        <is>
+          <t>AI产业链</t>
+        </is>
+      </c>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>二季报正文未列港股代码；代码沿用此前HKEX/CSOP核验</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2前十名基金投资明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>164212</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>天弘全球新能源汽车股票(QDII-LOF)A/C</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>2026年第2季度报告</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>债券披露</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>固定收益</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>25国债19</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>25国债19</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>019792</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>境内债券</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>900000</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>909443.1</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>现金/债券</t>
+        </is>
+      </c>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>非权益</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>非权益底仓，用于还原资产配置</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607201827148844_1.pdf</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>D:\vcp_hunter\产业链投研\artifacts\fund_tracking\q2_2026_164212.pdf</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>2026Q2债券投资明细</t>
         </is>
       </c>
     </row>
@@ -7362,56 +9354,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>报告期</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>报告日期</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>比例口径</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>金额人民币</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>比例%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>占净值%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -7920,6 +9912,276 @@
       </c>
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>权益投资</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1647778275.36</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>权益净值占比见地区/行业配置：86.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>其中：普通股</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1582385428.23</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>其中：存托凭证</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>65392847.13</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>基金投资</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>129548575.25</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>两只CSOP 2x产品，合计按净值占比6.77%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>固定收益投资</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>909443.1</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>25国债19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>银行存款和结算备付金合计</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>128783987.25</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>其他资产</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>106240011.38</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>主要为应收申购款等</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>总资产占比</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>2013260292.34</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>总资产口径；净资产口径会受负债/应付款影响</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H17"/>
@@ -7936,50 +10198,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>报告期</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>报告日期</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>公允价值人民币</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>占基金资产净值%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>口径</t>
         </is>
@@ -8640,6 +10902,369 @@
         <v>90.22</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>GICS/NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>845928450.6799999</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>685614842.42</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>中国香港</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>116234982.26</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1647778275.36</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>基础材料</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>241578100</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>GICS/NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>工业</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>98167059.14</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>GICS/NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>消费者非必需品</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>28940690.04</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>GICS/NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>信息技术</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>1278484088</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>GICS/NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>383765.49</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>GICS/NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>其他-GICS未分类</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>224572.69</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>GICS/NAV占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>1647778275.36</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>GICS/NAV占比</t>
         </is>
@@ -8660,208 +11285,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>2025年报%</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>2026Q1%</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>变化pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>2026Q2%</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Q2较Q1变化pct</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>解读</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>信息技术行业NAV占比</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="15" t="n">
         <v>38.83</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="15" t="n">
         <v>54.21</v>
       </c>
-      <c r="D2" s="5" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Q1显著加大AI/半导体/光通信方向暴露</t>
+      <c r="D2" s="15" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Q2继续明显转向AI硬件/半导体链，信息技术权重进一步提升</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>基础材料行业NAV占比</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="15" t="n">
         <v>15.2</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="15" t="n">
         <v>4.77</v>
       </c>
-      <c r="D3" s="7" t="n">
-        <v>-10.43</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锂资源/材料权重显著下降</t>
+      <c r="D3" s="15" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Q2材料/上游权重回升，但已经不是单纯锂资源主导</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>美国权益NAV占比</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="15" t="n">
         <v>51.94</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="15" t="n">
         <v>53.44</v>
       </c>
-      <c r="D4" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>海外科技保持高权重</t>
+      <c r="D4" s="15" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>美股仍为最大单一市场，但Q2中国/香港相关权益和基金投资贡献提高</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>中国权益NAV占比</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="15" t="n">
         <v>35.39</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="15" t="n">
         <v>27.89</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>A股电动化/资源品相对下降</t>
+      <c r="D5" s="15" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>A股/中国交易所权益权重回升</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>中国香港权益NAV占比</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="15" t="n">
         <v>5.96</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="15" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>港股权益增加；另有香港上市CSOP 2x基金投资</t>
+      <c r="D6" s="15" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>股票地区口径下降；另有香港上市CSOP 2x基金投资不在股票地区表内</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>基金投资NAV占比</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="15" t="n">
         <v>3.6</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Q1新增SK Hynix/Samsung 2x杠杆产品</t>
+      <c r="D7" s="15" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>两只CSOP 2x产品仍在，且合计净值占比提高到6.77%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>前十大股票NAV占比</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="15" t="n">
         <v>47.6</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="15" t="n">
         <v>37.55</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>-10.05</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>季度只披露前十大，组合可能更分散；不可直接理解为降仓</t>
+      <c r="D8" s="15" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>季度只披露前十大；Q2前十大更分散，不能推断总权益降到29.02%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>可见AI硬件链权重</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="15" t="n">
         <v>26.46</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="15" t="n">
         <v>37.58</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2025年报按NVDA/AVGO/TSM/LITE/LRCX计；Q1按前十大除TSLA并加两只2x计</t>
+      <c r="D9" s="15" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Q2按前十大股票+两只2x产品粗略统计；存储/HBM和半导体设备权重更直接</t>
         </is>
       </c>
     </row>
@@ -9755,430 +12410,526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>标的</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>主题</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>为何观察</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>来自报告</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>康宁</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>光通信/玻璃材料</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>Q2第一大股票，受AI数据中心光通信/材料链和汽车玻璃共同驱动</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>迈威尔科技</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>ASIC/高速互联芯片</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Q2新进第二大股票，AI网络和定制芯片弹性高</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>美光科技</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>存储/HBM</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Q2新进第三大股票，叠加存储涨价和AI HBM逻辑</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>AI算力/半导体</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Q1/Q2均在前十大，权重3.31%</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>2026Q1/Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>泰瑞达</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>半导体测试设备</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Q2仍在前十大但权重下降至2.24%</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>2026Q1/Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Lumentum</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>光通信/激光器</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Q2仍在前十大但权重下降至2.20%</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>2025年报/Q1/Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>应用材料</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>半导体设备</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Q2新进前十大，确认半导体设备链暴露</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Coherent</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>光通信/材料器件</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Q2仍在前十大，权重2.03%</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>2026Q1/Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>意法半导体</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>美国/欧洲</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>功率半导体/车规芯片</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Q2新进前十大，对应车规芯片和功率半导体涨价逻辑</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>华虹半导体</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>01347.HK</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>港股</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>特色工艺/功率半导体</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Q2新进前十大，香港市场稀缺链条标的</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>SK Hynix 2x</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>7709.HK</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>存储/HBM杠杆</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Q2基金投资第一大，净值占比4.87%</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>2026Q1/Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Samsung 2x</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>7747.HK / 9747.HK</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>存储/半导体杠杆</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Q2基金投资第二大，净值占比1.90%</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>2026Q1/Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>英伟达</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>美国</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>AI算力</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>核心AI beta；年报/Q1均为重仓</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2025年报/Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Q2退出前十大；后续观察是否降为隐藏持仓或已显著调出</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>2025年报/Q1，Q2未进前十大</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>台积电ADR</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>TSM</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>美国ADR</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>半导体代工</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>AI芯片制造链</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2025年报/Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Lumentum</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Q2退出前十大；后续观察是否降为隐藏持仓或已显著调出</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>2025年报/Q1，Q2未进前十大</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>博通</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>美国</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>光通信/传感</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Q1升至第三大股票</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2025年报/Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>泰瑞达</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>TER</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>半导体测试设备</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Q1新进前十大</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>KLAC</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Q1新进前十大</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Coherent</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>COHR</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>光通信/材料器件</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Q1新进前十大</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>AI算力/半导体</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Q1新进前十大</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2025年报/Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>拉姆研究</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>美国</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>半导体设备</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>年报/Q1均为前十大</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2025年报/Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SK Hynix 2x</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>07709.HK</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>香港</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>存储/HBM杠杆</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Q1新增2x产品，净值弹性高</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Samsung 2x</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>07747.HK / 09747.HK</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>香港</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>存储/半导体杠杆</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Q1新增2x产品，净值弹性高</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>宁德时代</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>A股</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>动力电池/储能</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>年报前十大，Q1退出前十大，观察是否继续下降</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2025年报</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>华友钴业</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>603799</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>A股</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>电池材料/资源</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>年报前十大，Q1退出前十大，观察材料链是否回升</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2025年报</t>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>AI半导体/连接</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Q2退出前十大；后续观察是否降为隐藏持仓或已显著调出</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>2025年报/Q1，Q2未进前十大</t>
         </is>
       </c>
     </row>
@@ -10197,1456 +12948,656 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>币种</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>估算权重%</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>是否固定</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>来源/说明</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>默认估算启用</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>英伟达</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>康宁(Corning)</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E2" s="11" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="E2" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>台积电ADR</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>迈威尔科技</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="E3" s="15" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>美光科技</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>美国超威半导体公司</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>泰瑞达</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>LITE</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Lumentum</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Lumentum Holdings Inc</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="E7" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>TER</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Teradyne</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>应用材料</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="E8" s="15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>KLAC</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Coherent Corp</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="E9" s="15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>意法半导体</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="E10" s="15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>博通</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>01347.HK</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>华虹半导体有限公司</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十大股票/存托凭证，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>COHR</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Coherent</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>7709.HK</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>CSOP SK Hynix Daily 2x Leveraged Product</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十名基金投资，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>7747.HK / 9747.HK</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>CSOP Samsung Electronics Daily 2x Leveraged Product</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2季报前十名基金投资，权重为NAV占比</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Lam Research</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Q2正式披露锚点</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>019792</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>25国债19</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>2026Q2债券投资，短期净值估算中按低波动处理</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>7709.HK</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>CSOP SK Hynix 2x</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Q2未披露权益桶</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>UNDISCLOSED_EQUITY_BUCKET</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>未披露权益持仓合计</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Q2权益NAV 86.07% - 前十大股票29.02%；个股待中报或重新拟合</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定锚点</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>7747.HK</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>CSOP Samsung 2x</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露前十大股票/两只ETF，权重锁定</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Q1固定债券</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>102298</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>国债2508</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Q1披露债券；短期净值拟合中按0日收益处理</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>000660.KS</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>SK hynix</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>现金/其他净敞口</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>CASH_OTHER_NET</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>现金、应收应付和其他净敞口</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>CNY/MIXED</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>002466.SZ</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>TIANQI LITHIUM CORPORATION</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>089030.KQ</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Techwing</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>247540.KQ</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>ECOPROBM</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>600563.SS</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>600563.SS</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>605376.SS</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>JIANGSU BOQIAN NEW MATERIALS ST</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>688052.SS</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>SUZHOU NOVOSENSE MICROELECTRONI</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>688559.SS</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>688559.SS</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>CRDO</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Credo Technology Group Holding </t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Micron Technology, Inc.</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>NBIS</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Nebius Group N.V.</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>SERV</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Serve Robotics Inc.</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>WOLF</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Wolfspeed, Inc.</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>300679.SZ</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>300679.SZ</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>3.00349887</v>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>002738.SZ</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>SINOMINE RESOURCE GROUP CO LTD</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>2.72762467</v>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>300450.SZ</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>WUXI LEAD INTELLIGENT EQUIPMENT</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>2.53947223</v>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Western Digital Corporation</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>2.52275336</v>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Vertiv Holdings, LLC</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>2.50739347</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>002138.SZ</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>002138.SZ</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>0.94293403</v>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>002497.SZ</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SICHUAN YAHUA INDUSTRIAL GROUP </t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>0.69314041</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>年报/交易披露候选</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>002407.SZ</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>DO-FLUORIDE NEW MATERIALS CO LT</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>0.63772566</v>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Q2新增披露外候选</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>ASML</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>ASML Holding N.V. - New York Re</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>0.33545731</v>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>LP最小化10日最大误差；单只&lt;=3.27%</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>100% - 权益86.07% - 基金投资6.77% - 债券0.05%；用于低波动余项</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>

--- a/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
+++ b/artifacts/fund_tracking/天弘全球新能源汽车QDII_LOF_164212_持仓跟踪.xlsx
@@ -27,6 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'对比摘要'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'后续跟踪模板'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'重点观察标的'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'持仓基金公告检查'!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1370,7 +1371,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
@@ -1405,7 +1406,7 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>已更新164212跟踪表Q2持仓/配置/观察/估算锚点</t>
+          <t>已更新164212专属跟踪表Q2持仓</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
@@ -1417,7 +1418,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -1452,7 +1453,7 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>同一投资组合；已随164212更新</t>
+          <t>已更新164212专属跟踪表Q2持仓</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
@@ -1464,7 +1465,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
@@ -1479,39 +1480,39 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>富国全球科技互联网股票型证券投资基金(QDII)二0二六年第1季度报告</t>
+          <t>富国全球科技互联网股票型证券投资基金(QDII)二0二六年第2季度报告</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+          <t>已更新统一持仓基金2026Q2跟踪表</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>https://fundf10.eastmoney.com/jjgg_100055.html</t>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607211827194882_1.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -1526,39 +1527,39 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>富国全球科技互联网股票型证券投资基金(QDII)二0二六年第1季度报告</t>
+          <t>富国全球科技互联网股票型证券投资基金(QDII)二0二六年第2季度报告</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+          <t>已更新统一持仓基金2026Q2跟踪表</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>https://fundf10.eastmoney.com/jjgg_022184.html</t>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607211827194882_1.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -1573,39 +1574,39 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>嘉实全球产业升级股票型发起式证券投资基金(QDII)2026年第1季度报告</t>
+          <t>嘉实全球产业升级股票型发起式证券投资基金(QDII)2026年第2季度报告</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+          <t>已更新统一持仓基金2026Q2跟踪表</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>https://fundf10.eastmoney.com/jjgg_017730.html</t>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607211827195101_1.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -1620,39 +1621,39 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>嘉实全球产业升级股票型发起式证券投资基金(QDII)2026年第1季度报告</t>
+          <t>嘉实全球产业升级股票型发起式证券投资基金(QDII)2026年第2季度报告</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+          <t>已更新统一持仓基金2026Q2跟踪表</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>https://fundf10.eastmoney.com/jjgg_017731.html</t>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607211827195101_1.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -1667,39 +1668,39 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>天弘全球高端制造混合型证券投资基金(QDII)2026年第1季度报告</t>
+          <t>天弘全球高端制造混合型证券投资基金(QDII)2026年第2季度报告</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+          <t>已更新统一持仓基金2026Q2跟踪表</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>https://fundf10.eastmoney.com/jjgg_016664.html</t>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607211827183829_1.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>2026-07-20 21:53:45</t>
+          <t>2026-07-21 12:25:11 +08:00</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1714,36 +1715,47 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>天弘全球高端制造混合型证券投资基金(QDII)2026年第1季度报告</t>
+          <t>天弘全球高端制造混合型证券投资基金(QDII)2026年第2季度报告</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>未发现2026Q2持仓披露；不更新持仓明细</t>
+          <t>已更新统一持仓基金2026Q2跟踪表</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>https://fundf10.eastmoney.com/jjgg_016665.html</t>
+          <t>https://pdf.dfcfw.com/pdf/H2_AN202607211827183829_1.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I9"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1913,7 +1925,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
